--- a/backend/data/financials_by_company/1486.HK.xlsx
+++ b/backend/data/financials_by_company/1486.HK.xlsx
@@ -662,197 +662,199 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-231601.215369</v>
+        <v>-579315</v>
       </c>
       <c r="C2" t="n">
-        <v>0.057828</v>
+        <v>0.165</v>
       </c>
       <c r="D2" t="n">
-        <v>18760000</v>
+        <v>77897000</v>
       </c>
       <c r="E2" t="n">
-        <v>-4005000</v>
+        <v>-3511000</v>
       </c>
       <c r="F2" t="n">
-        <v>-4005000</v>
+        <v>-3511000</v>
       </c>
       <c r="G2" t="n">
-        <v>-14851000</v>
+        <v>-1139000</v>
       </c>
       <c r="H2" t="n">
-        <v>23146000</v>
+        <v>59463000</v>
       </c>
       <c r="I2" t="n">
-        <v>339060000</v>
+        <v>699260000</v>
       </c>
       <c r="J2" t="n">
-        <v>14755000</v>
+        <v>74386000</v>
       </c>
       <c r="K2" t="n">
-        <v>-8391000</v>
+        <v>14923000</v>
       </c>
       <c r="L2" t="n">
-        <v>-5638000</v>
+        <v>-3680000</v>
       </c>
       <c r="M2" t="n">
-        <v>6913000</v>
+        <v>5160000</v>
       </c>
       <c r="N2" t="n">
-        <v>1275000</v>
+        <v>1480000</v>
       </c>
       <c r="O2" t="n">
-        <v>-11077601.215369</v>
+        <v>1792685</v>
       </c>
       <c r="P2" t="n">
-        <v>-14851000</v>
+        <v>-1139000</v>
       </c>
       <c r="Q2" t="n">
-        <v>411474000</v>
+        <v>849622000</v>
       </c>
       <c r="R2" t="n">
-        <v>368804233</v>
+        <v>369316344</v>
       </c>
       <c r="S2" t="n">
         <v>368804233</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.040253</v>
+        <v>-0.003126</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.040253</v>
+        <v>-0.003126</v>
       </c>
       <c r="V2" t="n">
-        <v>-14851000</v>
+        <v>-1139000</v>
       </c>
       <c r="W2" t="n">
-        <v>-14851000</v>
+        <v>-1139000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-14851000</v>
+        <v>-1139000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-432000</v>
+        <v>-5644000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-14419000</v>
-      </c>
-      <c r="AB2" t="n">
+        <v>4505000</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>4505000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>5258000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>9763000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>3178000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-2961000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-2246000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>5207000</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>0</v>
       </c>
-      <c r="AC2" t="n">
-        <v>-14419000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-885000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-15304000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1279000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-5773000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>2388000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>3385000</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="n">
-        <v>-5638000</v>
+        <v>-3680000</v>
       </c>
       <c r="AL2" t="n">
-        <v>6913000</v>
+        <v>5160000</v>
       </c>
       <c r="AM2" t="n">
-        <v>1275000</v>
+        <v>1480000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-10171000</v>
+        <v>12368000</v>
       </c>
       <c r="AO2" t="n">
-        <v>72414000</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
+        <v>150362000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>-1498000</v>
+      </c>
       <c r="AQ2" t="n">
-        <v>74971000</v>
+        <v>154278000</v>
       </c>
       <c r="AR2" t="n">
-        <v>74971000</v>
+        <v>154278000</v>
       </c>
       <c r="AS2" t="n">
-        <v>62243000</v>
+        <v>162730000</v>
       </c>
       <c r="AT2" t="n">
-        <v>339060000</v>
+        <v>699260000</v>
       </c>
       <c r="AU2" t="n">
-        <v>401303000</v>
+        <v>861990000</v>
       </c>
       <c r="AV2" t="n">
-        <v>401303000</v>
+        <v>861990000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-441818.875743</v>
+        <v>-191242.973385</v>
       </c>
       <c r="C3" t="n">
-        <v>0.071261</v>
+        <v>0.031413</v>
       </c>
       <c r="D3" t="n">
-        <v>8660000</v>
+        <v>24504000</v>
       </c>
       <c r="E3" t="n">
-        <v>-6200000</v>
+        <v>-6088000</v>
       </c>
       <c r="F3" t="n">
-        <v>-6200000</v>
+        <v>-6088000</v>
       </c>
       <c r="G3" t="n">
-        <v>-36228000</v>
+        <v>-37539000</v>
       </c>
       <c r="H3" t="n">
-        <v>32581000</v>
+        <v>44675000</v>
       </c>
       <c r="I3" t="n">
-        <v>395708000</v>
+        <v>462336000</v>
       </c>
       <c r="J3" t="n">
-        <v>2460000</v>
+        <v>18416000</v>
       </c>
       <c r="K3" t="n">
-        <v>-30121000</v>
+        <v>-26259000</v>
       </c>
       <c r="L3" t="n">
-        <v>-5928000</v>
+        <v>-3299000</v>
       </c>
       <c r="M3" t="n">
-        <v>6561000</v>
+        <v>4588000</v>
       </c>
       <c r="N3" t="n">
-        <v>633000</v>
+        <v>1289000</v>
       </c>
       <c r="O3" t="n">
-        <v>-30469818.875743</v>
+        <v>-31642242.973385</v>
       </c>
       <c r="P3" t="n">
-        <v>-21240000</v>
+        <v>-18797000</v>
       </c>
       <c r="Q3" t="n">
-        <v>481269000</v>
+        <v>555121000</v>
       </c>
       <c r="R3" t="n">
         <v>368804233</v>
@@ -861,140 +863,142 @@
         <v>368804233</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.057605</v>
+        <v>-0.050961</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.057605</v>
+        <v>-0.050961</v>
       </c>
       <c r="V3" t="n">
-        <v>-21240000</v>
+        <v>-18797000</v>
       </c>
       <c r="W3" t="n">
-        <v>-21240000</v>
+        <v>-18797000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-21240000</v>
+        <v>-18797000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-2160000</v>
+        <v>-7661000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-19080000</v>
+        <v>-11136000</v>
       </c>
       <c r="AB3" t="n">
-        <v>14988000</v>
+        <v>18742000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-34068000</v>
+        <v>-29878000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-2614000</v>
+        <v>-969000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-36682000</v>
+        <v>-30847000</v>
       </c>
       <c r="AF3" t="n">
-        <v>2130000</v>
+        <v>1768000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-6713000</v>
+        <v>-3239000</v>
       </c>
       <c r="AH3" t="n">
-        <v>1118000</v>
+        <v>-191000</v>
       </c>
       <c r="AI3" t="n">
-        <v>5595000</v>
+        <v>3430000</v>
       </c>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="n">
-        <v>-5928000</v>
+        <v>-3299000</v>
       </c>
       <c r="AL3" t="n">
-        <v>6561000</v>
+        <v>4588000</v>
       </c>
       <c r="AM3" t="n">
-        <v>633000</v>
+        <v>1289000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-27019000</v>
+        <v>-21362000</v>
       </c>
       <c r="AO3" t="n">
-        <v>85561000</v>
-      </c>
-      <c r="AP3" t="inlineStr"/>
+        <v>92785000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>-894000</v>
+      </c>
       <c r="AQ3" t="n">
-        <v>89487000</v>
+        <v>102125000</v>
       </c>
       <c r="AR3" t="n">
-        <v>89487000</v>
+        <v>102125000</v>
       </c>
       <c r="AS3" t="n">
-        <v>58542000</v>
+        <v>71423000</v>
       </c>
       <c r="AT3" t="n">
-        <v>395708000</v>
+        <v>462336000</v>
       </c>
       <c r="AU3" t="n">
-        <v>454250000</v>
+        <v>533759000</v>
       </c>
       <c r="AV3" t="n">
-        <v>454250000</v>
+        <v>533759000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-191242.973385</v>
+        <v>-441818.875743</v>
       </c>
       <c r="C4" t="n">
-        <v>0.031413</v>
+        <v>0.071261</v>
       </c>
       <c r="D4" t="n">
-        <v>24504000</v>
+        <v>8660000</v>
       </c>
       <c r="E4" t="n">
-        <v>-6088000</v>
+        <v>-6200000</v>
       </c>
       <c r="F4" t="n">
-        <v>-6088000</v>
+        <v>-6200000</v>
       </c>
       <c r="G4" t="n">
-        <v>-37539000</v>
+        <v>-36228000</v>
       </c>
       <c r="H4" t="n">
-        <v>44675000</v>
+        <v>32581000</v>
       </c>
       <c r="I4" t="n">
-        <v>462336000</v>
+        <v>395708000</v>
       </c>
       <c r="J4" t="n">
-        <v>18416000</v>
+        <v>2460000</v>
       </c>
       <c r="K4" t="n">
-        <v>-26259000</v>
+        <v>-30121000</v>
       </c>
       <c r="L4" t="n">
-        <v>-3299000</v>
+        <v>-5928000</v>
       </c>
       <c r="M4" t="n">
-        <v>4588000</v>
+        <v>6561000</v>
       </c>
       <c r="N4" t="n">
-        <v>1289000</v>
+        <v>633000</v>
       </c>
       <c r="O4" t="n">
-        <v>-31642242.973385</v>
+        <v>-30469818.875743</v>
       </c>
       <c r="P4" t="n">
-        <v>-18797000</v>
+        <v>-21240000</v>
       </c>
       <c r="Q4" t="n">
-        <v>555121000</v>
+        <v>481269000</v>
       </c>
       <c r="R4" t="n">
         <v>368804233</v>
@@ -1003,233 +1007,229 @@
         <v>368804233</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.050961</v>
+        <v>-0.057605</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.050961</v>
+        <v>-0.057605</v>
       </c>
       <c r="V4" t="n">
-        <v>-18797000</v>
+        <v>-21240000</v>
       </c>
       <c r="W4" t="n">
-        <v>-18797000</v>
+        <v>-21240000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-18797000</v>
+        <v>-21240000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-7661000</v>
+        <v>-2160000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-11136000</v>
+        <v>-19080000</v>
       </c>
       <c r="AB4" t="n">
-        <v>18742000</v>
+        <v>14988000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-29878000</v>
+        <v>-34068000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-969000</v>
+        <v>-2614000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-30847000</v>
+        <v>-36682000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1768000</v>
+        <v>2130000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-3239000</v>
+        <v>-6713000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-191000</v>
+        <v>1118000</v>
       </c>
       <c r="AI4" t="n">
-        <v>3430000</v>
+        <v>5595000</v>
       </c>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>-3299000</v>
+        <v>-5928000</v>
       </c>
       <c r="AL4" t="n">
-        <v>4588000</v>
+        <v>6561000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1289000</v>
+        <v>633000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-21362000</v>
+        <v>-27019000</v>
       </c>
       <c r="AO4" t="n">
-        <v>92785000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>-894000</v>
-      </c>
+        <v>85561000</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
-        <v>102125000</v>
+        <v>89487000</v>
       </c>
       <c r="AR4" t="n">
-        <v>102125000</v>
+        <v>89487000</v>
       </c>
       <c r="AS4" t="n">
-        <v>71423000</v>
+        <v>58542000</v>
       </c>
       <c r="AT4" t="n">
-        <v>462336000</v>
+        <v>395708000</v>
       </c>
       <c r="AU4" t="n">
-        <v>533759000</v>
+        <v>454250000</v>
       </c>
       <c r="AV4" t="n">
-        <v>533759000</v>
+        <v>454250000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-579315</v>
+        <v>-231601.215369</v>
       </c>
       <c r="C5" t="n">
-        <v>0.165</v>
+        <v>0.057828</v>
       </c>
       <c r="D5" t="n">
-        <v>77897000</v>
+        <v>18760000</v>
       </c>
       <c r="E5" t="n">
-        <v>-3511000</v>
+        <v>-4005000</v>
       </c>
       <c r="F5" t="n">
-        <v>-3511000</v>
+        <v>-4005000</v>
       </c>
       <c r="G5" t="n">
-        <v>-1139000</v>
+        <v>-14851000</v>
       </c>
       <c r="H5" t="n">
-        <v>59463000</v>
+        <v>23146000</v>
       </c>
       <c r="I5" t="n">
-        <v>699260000</v>
+        <v>339060000</v>
       </c>
       <c r="J5" t="n">
-        <v>74386000</v>
+        <v>14755000</v>
       </c>
       <c r="K5" t="n">
-        <v>14923000</v>
+        <v>-8391000</v>
       </c>
       <c r="L5" t="n">
-        <v>-3680000</v>
+        <v>-5638000</v>
       </c>
       <c r="M5" t="n">
-        <v>5160000</v>
+        <v>6913000</v>
       </c>
       <c r="N5" t="n">
-        <v>1480000</v>
+        <v>1275000</v>
       </c>
       <c r="O5" t="n">
-        <v>1792685</v>
+        <v>-11077601.215369</v>
       </c>
       <c r="P5" t="n">
-        <v>-1139000</v>
+        <v>-14851000</v>
       </c>
       <c r="Q5" t="n">
-        <v>849622000</v>
+        <v>411474000</v>
       </c>
       <c r="R5" t="n">
-        <v>369316344</v>
+        <v>368804233</v>
       </c>
       <c r="S5" t="n">
         <v>368804233</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.003126</v>
+        <v>-0.040253</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.003126</v>
+        <v>-0.040253</v>
       </c>
       <c r="V5" t="n">
-        <v>-1139000</v>
+        <v>-14851000</v>
       </c>
       <c r="W5" t="n">
-        <v>-1139000</v>
+        <v>-14851000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1139000</v>
+        <v>-14851000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-5644000</v>
+        <v>-432000</v>
       </c>
       <c r="AA5" t="n">
-        <v>4505000</v>
-      </c>
-      <c r="AB5" t="inlineStr"/>
+        <v>-14419000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
       <c r="AC5" t="n">
-        <v>4505000</v>
+        <v>-14419000</v>
       </c>
       <c r="AD5" t="n">
-        <v>5258000</v>
+        <v>-885000</v>
       </c>
       <c r="AE5" t="n">
-        <v>9763000</v>
+        <v>-15304000</v>
       </c>
       <c r="AF5" t="n">
-        <v>3178000</v>
+        <v>1279000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-2961000</v>
+        <v>-5773000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-2246000</v>
+        <v>2388000</v>
       </c>
       <c r="AI5" t="n">
-        <v>5207000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
+        <v>3385000</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="n">
-        <v>-3680000</v>
+        <v>-5638000</v>
       </c>
       <c r="AL5" t="n">
-        <v>5160000</v>
+        <v>6913000</v>
       </c>
       <c r="AM5" t="n">
-        <v>1480000</v>
+        <v>1275000</v>
       </c>
       <c r="AN5" t="n">
-        <v>12368000</v>
+        <v>-10171000</v>
       </c>
       <c r="AO5" t="n">
-        <v>150362000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-1498000</v>
-      </c>
+        <v>72414000</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>154278000</v>
+        <v>74971000</v>
       </c>
       <c r="AR5" t="n">
-        <v>154278000</v>
+        <v>74971000</v>
       </c>
       <c r="AS5" t="n">
-        <v>162730000</v>
+        <v>62243000</v>
       </c>
       <c r="AT5" t="n">
-        <v>699260000</v>
+        <v>339060000</v>
       </c>
       <c r="AU5" t="n">
-        <v>861990000</v>
+        <v>401303000</v>
       </c>
       <c r="AV5" t="n">
-        <v>861990000</v>
+        <v>401303000</v>
       </c>
     </row>
   </sheetData>
@@ -1580,7 +1580,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>368804233</v>
@@ -1588,47 +1588,45 @@
       <c r="C2" t="n">
         <v>368804233</v>
       </c>
-      <c r="D2" t="n">
-        <v>12363000</v>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>97527000</v>
+        <v>183751000</v>
       </c>
       <c r="F2" t="n">
-        <v>391976000</v>
+        <v>441823000</v>
       </c>
       <c r="G2" t="n">
-        <v>483373000</v>
+        <v>545237000</v>
       </c>
       <c r="H2" t="n">
-        <v>253448000</v>
+        <v>422984000</v>
       </c>
       <c r="I2" t="n">
-        <v>391976000</v>
+        <v>441823000</v>
       </c>
       <c r="J2" t="n">
-        <v>10561000</v>
+        <v>107426000</v>
       </c>
       <c r="K2" t="n">
-        <v>396407000</v>
+        <v>468912000</v>
       </c>
       <c r="L2" t="n">
-        <v>396770000</v>
+        <v>471420000</v>
       </c>
       <c r="M2" t="n">
-        <v>399063000</v>
+        <v>522052000</v>
       </c>
       <c r="N2" t="n">
-        <v>2656000</v>
+        <v>53140000</v>
       </c>
       <c r="O2" t="n">
-        <v>396407000</v>
+        <v>468912000</v>
       </c>
       <c r="P2" t="n">
-        <v>8986000</v>
+        <v>33610000</v>
       </c>
       <c r="Q2" t="n">
-        <v>154324000</v>
+        <v>176250000</v>
       </c>
       <c r="R2" t="n">
         <v>283501000</v>
@@ -1640,142 +1638,138 @@
         <v>2883000</v>
       </c>
       <c r="U2" t="n">
-        <v>220822000</v>
+        <v>381472000</v>
       </c>
       <c r="V2" t="n">
-        <v>5835000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2160000</v>
-      </c>
+        <v>75926000</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
-        <v>1156000</v>
+        <v>1249000</v>
       </c>
       <c r="Y2" t="n">
-        <v>2519000</v>
+        <v>74677000</v>
       </c>
       <c r="Z2" t="n">
-        <v>2156000</v>
+        <v>72169000</v>
       </c>
       <c r="AA2" t="n">
-        <v>363000</v>
+        <v>2508000</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>214987000</v>
+        <v>305546000</v>
       </c>
       <c r="AD2" t="n">
-        <v>95008000</v>
+        <v>109074000</v>
       </c>
       <c r="AE2" t="n">
-        <v>8405000</v>
+        <v>35257000</v>
       </c>
       <c r="AF2" t="n">
-        <v>86603000</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
+        <v>73817000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2160000</v>
+      </c>
       <c r="AH2" t="n">
-        <v>39885000</v>
+        <v>14631000</v>
       </c>
       <c r="AI2" t="n">
-        <v>9751000</v>
+        <v>7000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1150000</v>
+        <v>4711000</v>
       </c>
       <c r="AK2" t="n">
-        <v>28984000</v>
+        <v>9913000</v>
       </c>
       <c r="AL2" t="n">
-        <v>619885000</v>
+        <v>903524000</v>
       </c>
       <c r="AM2" t="n">
-        <v>151450000</v>
+        <v>174994000</v>
       </c>
       <c r="AN2" t="n">
-        <v>11823000</v>
+        <v>11870000</v>
       </c>
       <c r="AO2" t="n">
-        <v>15226000</v>
+        <v>6726000</v>
       </c>
       <c r="AP2" t="n">
-        <v>104419000</v>
+        <v>4511000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2656000</v>
+        <v>4156000</v>
       </c>
       <c r="AR2" t="n">
-        <v>101763000</v>
+        <v>355000</v>
       </c>
       <c r="AS2" t="n">
-        <v>4431000</v>
+        <v>27089000</v>
       </c>
       <c r="AT2" t="n">
-        <v>280000</v>
+        <v>11434000</v>
       </c>
       <c r="AU2" t="n">
-        <v>4151000</v>
+        <v>15655000</v>
       </c>
       <c r="AV2" t="n">
-        <v>15551000</v>
+        <v>124798000</v>
       </c>
       <c r="AW2" t="n">
-        <v>-204880000</v>
+        <v>-170656000</v>
       </c>
       <c r="AX2" t="n">
-        <v>220431000</v>
+        <v>295454000</v>
       </c>
       <c r="AY2" t="n">
-        <v>138585000</v>
+        <v>199163000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>59738000</v>
+        <v>68381000</v>
       </c>
       <c r="BA2" t="n">
-        <v>22108000</v>
+        <v>27910000</v>
       </c>
       <c r="BB2" t="n">
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>468435000</v>
-      </c>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="n">
-        <v>4492000</v>
-      </c>
-      <c r="BF2" t="inlineStr"/>
+        <v>728530000</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>18701000</v>
+      </c>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="n">
+        <v>57979000</v>
+      </c>
       <c r="BG2" t="n">
-        <v>248322000</v>
+        <v>283124000</v>
       </c>
       <c r="BH2" t="n">
-        <v>133039000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>-12145000</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>145184000</v>
-      </c>
+        <v>230075000</v>
+      </c>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
       <c r="BK2" t="n">
-        <v>82582000</v>
+        <v>215331000</v>
       </c>
       <c r="BL2" t="n">
-        <v>7979000</v>
+        <v>17203000</v>
       </c>
       <c r="BM2" t="n">
-        <v>74603000</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>32350000</v>
-      </c>
+        <v>198128000</v>
+      </c>
+      <c r="BN2" t="inlineStr"/>
       <c r="BO2" t="n">
-        <v>42253000</v>
+        <v>198128000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>368804233</v>
@@ -1785,43 +1779,43 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>118843000</v>
+        <v>147267000</v>
       </c>
       <c r="F3" t="n">
-        <v>411282000</v>
+        <v>412665000</v>
       </c>
       <c r="G3" t="n">
-        <v>504751000</v>
+        <v>524141000</v>
       </c>
       <c r="H3" t="n">
-        <v>276209000</v>
+        <v>421881000</v>
       </c>
       <c r="I3" t="n">
-        <v>411282000</v>
+        <v>412665000</v>
       </c>
       <c r="J3" t="n">
-        <v>29863000</v>
+        <v>61308000</v>
       </c>
       <c r="K3" t="n">
-        <v>415771000</v>
+        <v>438182000</v>
       </c>
       <c r="L3" t="n">
-        <v>416868000</v>
+        <v>440236000</v>
       </c>
       <c r="M3" t="n">
-        <v>417995000</v>
+        <v>505622000</v>
       </c>
       <c r="N3" t="n">
-        <v>2224000</v>
+        <v>67440000</v>
       </c>
       <c r="O3" t="n">
-        <v>415771000</v>
+        <v>438182000</v>
       </c>
       <c r="P3" t="n">
-        <v>24713000</v>
+        <v>28845000</v>
       </c>
       <c r="Q3" t="n">
-        <v>153448000</v>
+        <v>168482000</v>
       </c>
       <c r="R3" t="n">
         <v>283501000</v>
@@ -1833,142 +1827,140 @@
         <v>2883000</v>
       </c>
       <c r="U3" t="n">
-        <v>265203000</v>
+        <v>328581000</v>
       </c>
       <c r="V3" t="n">
-        <v>14921000</v>
+        <v>38157000</v>
       </c>
       <c r="W3" t="n">
         <v>2160000</v>
       </c>
       <c r="X3" t="n">
-        <v>1136000</v>
+        <v>440000</v>
       </c>
       <c r="Y3" t="n">
-        <v>11625000</v>
+        <v>35557000</v>
       </c>
       <c r="Z3" t="n">
-        <v>10528000</v>
+        <v>33503000</v>
       </c>
       <c r="AA3" t="n">
-        <v>1097000</v>
-      </c>
-      <c r="AB3" t="inlineStr"/>
+        <v>2054000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2160000</v>
+      </c>
       <c r="AC3" t="n">
-        <v>250282000</v>
+        <v>290424000</v>
       </c>
       <c r="AD3" t="n">
-        <v>107218000</v>
+        <v>111710000</v>
       </c>
       <c r="AE3" t="n">
-        <v>19335000</v>
+        <v>27805000</v>
       </c>
       <c r="AF3" t="n">
-        <v>87883000</v>
+        <v>83905000</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>41599000</v>
+        <v>26484000</v>
       </c>
       <c r="AI3" t="n">
-        <v>10191000</v>
+        <v>6549000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2393000</v>
+        <v>4163000</v>
       </c>
       <c r="AK3" t="n">
-        <v>29015000</v>
+        <v>15772000</v>
       </c>
       <c r="AL3" t="n">
-        <v>683198000</v>
+        <v>834203000</v>
       </c>
       <c r="AM3" t="n">
-        <v>156707000</v>
+        <v>121898000</v>
       </c>
       <c r="AN3" t="n">
-        <v>9553000</v>
+        <v>11260000</v>
       </c>
       <c r="AO3" t="n">
-        <v>13395000</v>
+        <v>8364000</v>
       </c>
       <c r="AP3" t="n">
-        <v>92856000</v>
+        <v>3986000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2851000</v>
+        <v>3822000</v>
       </c>
       <c r="AR3" t="n">
-        <v>90005000</v>
+        <v>164000</v>
       </c>
       <c r="AS3" t="n">
-        <v>4489000</v>
+        <v>25517000</v>
       </c>
       <c r="AT3" t="n">
-        <v>280000</v>
+        <v>10230000</v>
       </c>
       <c r="AU3" t="n">
-        <v>4209000</v>
+        <v>15287000</v>
       </c>
       <c r="AV3" t="n">
-        <v>36414000</v>
+        <v>72771000</v>
       </c>
       <c r="AW3" t="n">
-        <v>-186084000</v>
+        <v>-203528000</v>
       </c>
       <c r="AX3" t="n">
-        <v>222498000</v>
+        <v>276299000</v>
       </c>
       <c r="AY3" t="n">
-        <v>139448000</v>
+        <v>181927000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>60653000</v>
+        <v>67310000</v>
       </c>
       <c r="BA3" t="n">
-        <v>22397000</v>
+        <v>27062000</v>
       </c>
       <c r="BB3" t="n">
         <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>526491000</v>
+        <v>712305000</v>
       </c>
       <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="n">
+        <v>57490000</v>
+      </c>
       <c r="BG3" t="n">
-        <v>250784000</v>
+        <v>316462000</v>
       </c>
       <c r="BH3" t="n">
-        <v>178601000</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>-11689000</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>190290000</v>
-      </c>
+        <v>223000000</v>
+      </c>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
       <c r="BK3" t="n">
-        <v>97106000</v>
+        <v>172843000</v>
       </c>
       <c r="BL3" t="n">
-        <v>7005000</v>
+        <v>11974000</v>
       </c>
       <c r="BM3" t="n">
-        <v>90101000</v>
+        <v>160869000</v>
       </c>
       <c r="BN3" t="n">
-        <v>50412000</v>
+        <v>23880000</v>
       </c>
       <c r="BO3" t="n">
-        <v>39689000</v>
+        <v>136989000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>368804233</v>
@@ -1978,43 +1970,43 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>147267000</v>
+        <v>118843000</v>
       </c>
       <c r="F4" t="n">
-        <v>412665000</v>
+        <v>411282000</v>
       </c>
       <c r="G4" t="n">
-        <v>524141000</v>
+        <v>504751000</v>
       </c>
       <c r="H4" t="n">
-        <v>421881000</v>
+        <v>276209000</v>
       </c>
       <c r="I4" t="n">
-        <v>412665000</v>
+        <v>411282000</v>
       </c>
       <c r="J4" t="n">
-        <v>61308000</v>
+        <v>29863000</v>
       </c>
       <c r="K4" t="n">
-        <v>438182000</v>
+        <v>415771000</v>
       </c>
       <c r="L4" t="n">
-        <v>440236000</v>
+        <v>416868000</v>
       </c>
       <c r="M4" t="n">
-        <v>505622000</v>
+        <v>417995000</v>
       </c>
       <c r="N4" t="n">
-        <v>67440000</v>
+        <v>2224000</v>
       </c>
       <c r="O4" t="n">
-        <v>438182000</v>
+        <v>415771000</v>
       </c>
       <c r="P4" t="n">
-        <v>28845000</v>
+        <v>24713000</v>
       </c>
       <c r="Q4" t="n">
-        <v>168482000</v>
+        <v>153448000</v>
       </c>
       <c r="R4" t="n">
         <v>283501000</v>
@@ -2026,140 +2018,142 @@
         <v>2883000</v>
       </c>
       <c r="U4" t="n">
-        <v>328581000</v>
+        <v>265203000</v>
       </c>
       <c r="V4" t="n">
-        <v>38157000</v>
+        <v>14921000</v>
       </c>
       <c r="W4" t="n">
         <v>2160000</v>
       </c>
       <c r="X4" t="n">
-        <v>440000</v>
+        <v>1136000</v>
       </c>
       <c r="Y4" t="n">
-        <v>35557000</v>
+        <v>11625000</v>
       </c>
       <c r="Z4" t="n">
-        <v>33503000</v>
+        <v>10528000</v>
       </c>
       <c r="AA4" t="n">
-        <v>2054000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2160000</v>
-      </c>
+        <v>1097000</v>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>290424000</v>
+        <v>250282000</v>
       </c>
       <c r="AD4" t="n">
-        <v>111710000</v>
+        <v>107218000</v>
       </c>
       <c r="AE4" t="n">
-        <v>27805000</v>
+        <v>19335000</v>
       </c>
       <c r="AF4" t="n">
-        <v>83905000</v>
+        <v>87883000</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>26484000</v>
+        <v>41599000</v>
       </c>
       <c r="AI4" t="n">
-        <v>6549000</v>
+        <v>10191000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>4163000</v>
+        <v>2393000</v>
       </c>
       <c r="AK4" t="n">
-        <v>15772000</v>
+        <v>29015000</v>
       </c>
       <c r="AL4" t="n">
-        <v>834203000</v>
+        <v>683198000</v>
       </c>
       <c r="AM4" t="n">
-        <v>121898000</v>
+        <v>156707000</v>
       </c>
       <c r="AN4" t="n">
-        <v>11260000</v>
+        <v>9553000</v>
       </c>
       <c r="AO4" t="n">
-        <v>8364000</v>
+        <v>13395000</v>
       </c>
       <c r="AP4" t="n">
-        <v>3986000</v>
+        <v>92856000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3822000</v>
+        <v>2851000</v>
       </c>
       <c r="AR4" t="n">
-        <v>164000</v>
+        <v>90005000</v>
       </c>
       <c r="AS4" t="n">
-        <v>25517000</v>
+        <v>4489000</v>
       </c>
       <c r="AT4" t="n">
-        <v>10230000</v>
+        <v>280000</v>
       </c>
       <c r="AU4" t="n">
-        <v>15287000</v>
+        <v>4209000</v>
       </c>
       <c r="AV4" t="n">
-        <v>72771000</v>
+        <v>36414000</v>
       </c>
       <c r="AW4" t="n">
-        <v>-203528000</v>
+        <v>-186084000</v>
       </c>
       <c r="AX4" t="n">
-        <v>276299000</v>
+        <v>222498000</v>
       </c>
       <c r="AY4" t="n">
-        <v>181927000</v>
+        <v>139448000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>67310000</v>
+        <v>60653000</v>
       </c>
       <c r="BA4" t="n">
-        <v>27062000</v>
+        <v>22397000</v>
       </c>
       <c r="BB4" t="n">
         <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>712305000</v>
+        <v>526491000</v>
       </c>
       <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="n">
-        <v>57490000</v>
-      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="n">
-        <v>316462000</v>
+        <v>250784000</v>
       </c>
       <c r="BH4" t="n">
-        <v>223000000</v>
-      </c>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
+        <v>178601000</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>-11689000</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>190290000</v>
+      </c>
       <c r="BK4" t="n">
-        <v>172843000</v>
+        <v>97106000</v>
       </c>
       <c r="BL4" t="n">
-        <v>11974000</v>
+        <v>7005000</v>
       </c>
       <c r="BM4" t="n">
-        <v>160869000</v>
+        <v>90101000</v>
       </c>
       <c r="BN4" t="n">
-        <v>23880000</v>
+        <v>50412000</v>
       </c>
       <c r="BO4" t="n">
-        <v>136989000</v>
+        <v>39689000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>368804233</v>
@@ -2167,45 +2161,47 @@
       <c r="C5" t="n">
         <v>368804233</v>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>12363000</v>
+      </c>
       <c r="E5" t="n">
-        <v>183751000</v>
+        <v>97527000</v>
       </c>
       <c r="F5" t="n">
-        <v>441823000</v>
+        <v>391976000</v>
       </c>
       <c r="G5" t="n">
-        <v>545237000</v>
+        <v>483373000</v>
       </c>
       <c r="H5" t="n">
-        <v>422984000</v>
+        <v>253448000</v>
       </c>
       <c r="I5" t="n">
-        <v>441823000</v>
+        <v>391976000</v>
       </c>
       <c r="J5" t="n">
-        <v>107426000</v>
+        <v>10561000</v>
       </c>
       <c r="K5" t="n">
-        <v>468912000</v>
+        <v>396407000</v>
       </c>
       <c r="L5" t="n">
-        <v>471420000</v>
+        <v>396770000</v>
       </c>
       <c r="M5" t="n">
-        <v>522052000</v>
+        <v>399063000</v>
       </c>
       <c r="N5" t="n">
-        <v>53140000</v>
+        <v>2656000</v>
       </c>
       <c r="O5" t="n">
-        <v>468912000</v>
+        <v>396407000</v>
       </c>
       <c r="P5" t="n">
-        <v>33610000</v>
+        <v>8986000</v>
       </c>
       <c r="Q5" t="n">
-        <v>176250000</v>
+        <v>154324000</v>
       </c>
       <c r="R5" t="n">
         <v>283501000</v>
@@ -2217,133 +2213,137 @@
         <v>2883000</v>
       </c>
       <c r="U5" t="n">
-        <v>381472000</v>
+        <v>220822000</v>
       </c>
       <c r="V5" t="n">
-        <v>75926000</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
+        <v>5835000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2160000</v>
+      </c>
       <c r="X5" t="n">
-        <v>1249000</v>
+        <v>1156000</v>
       </c>
       <c r="Y5" t="n">
-        <v>74677000</v>
+        <v>2519000</v>
       </c>
       <c r="Z5" t="n">
-        <v>72169000</v>
+        <v>2156000</v>
       </c>
       <c r="AA5" t="n">
-        <v>2508000</v>
+        <v>363000</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>305546000</v>
+        <v>214987000</v>
       </c>
       <c r="AD5" t="n">
-        <v>109074000</v>
+        <v>95008000</v>
       </c>
       <c r="AE5" t="n">
-        <v>35257000</v>
+        <v>8405000</v>
       </c>
       <c r="AF5" t="n">
-        <v>73817000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2160000</v>
-      </c>
+        <v>86603000</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>14631000</v>
+        <v>39885000</v>
       </c>
       <c r="AI5" t="n">
-        <v>7000</v>
+        <v>9751000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4711000</v>
+        <v>1150000</v>
       </c>
       <c r="AK5" t="n">
-        <v>9913000</v>
+        <v>28984000</v>
       </c>
       <c r="AL5" t="n">
-        <v>903524000</v>
+        <v>619885000</v>
       </c>
       <c r="AM5" t="n">
-        <v>174994000</v>
+        <v>151450000</v>
       </c>
       <c r="AN5" t="n">
-        <v>11870000</v>
+        <v>11823000</v>
       </c>
       <c r="AO5" t="n">
-        <v>6726000</v>
+        <v>15226000</v>
       </c>
       <c r="AP5" t="n">
-        <v>4511000</v>
+        <v>104419000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4156000</v>
+        <v>2656000</v>
       </c>
       <c r="AR5" t="n">
-        <v>355000</v>
+        <v>101763000</v>
       </c>
       <c r="AS5" t="n">
-        <v>27089000</v>
+        <v>4431000</v>
       </c>
       <c r="AT5" t="n">
-        <v>11434000</v>
+        <v>280000</v>
       </c>
       <c r="AU5" t="n">
-        <v>15655000</v>
+        <v>4151000</v>
       </c>
       <c r="AV5" t="n">
-        <v>124798000</v>
+        <v>15551000</v>
       </c>
       <c r="AW5" t="n">
-        <v>-170656000</v>
+        <v>-204880000</v>
       </c>
       <c r="AX5" t="n">
-        <v>295454000</v>
+        <v>220431000</v>
       </c>
       <c r="AY5" t="n">
-        <v>199163000</v>
+        <v>138585000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>68381000</v>
+        <v>59738000</v>
       </c>
       <c r="BA5" t="n">
-        <v>27910000</v>
+        <v>22108000</v>
       </c>
       <c r="BB5" t="n">
         <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>728530000</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>18701000</v>
-      </c>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="n">
-        <v>57979000</v>
-      </c>
+        <v>468435000</v>
+      </c>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="n">
+        <v>4492000</v>
+      </c>
+      <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="n">
-        <v>283124000</v>
+        <v>248322000</v>
       </c>
       <c r="BH5" t="n">
-        <v>230075000</v>
-      </c>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
+        <v>133039000</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>-12145000</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>145184000</v>
+      </c>
       <c r="BK5" t="n">
-        <v>215331000</v>
+        <v>82582000</v>
       </c>
       <c r="BL5" t="n">
-        <v>17203000</v>
+        <v>7979000</v>
       </c>
       <c r="BM5" t="n">
-        <v>198128000</v>
-      </c>
-      <c r="BN5" t="inlineStr"/>
+        <v>74603000</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>32350000</v>
+      </c>
       <c r="BO5" t="n">
-        <v>198128000</v>
+        <v>42253000</v>
       </c>
     </row>
   </sheetData>
@@ -2594,560 +2594,560 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>13728000</v>
+        <v>-22748000</v>
       </c>
       <c r="C2" t="n">
-        <v>-28014000</v>
+        <v>-39450000</v>
       </c>
       <c r="D2" t="n">
-        <v>26000000</v>
+        <v>55193000</v>
       </c>
       <c r="E2" t="n">
-        <v>-2864000</v>
+        <v>-18553000</v>
       </c>
       <c r="F2" t="n">
-        <v>53319000</v>
+        <v>198128000</v>
       </c>
       <c r="G2" t="n">
-        <v>46021000</v>
+        <v>228412000</v>
       </c>
       <c r="H2" t="n">
-        <v>-1598000</v>
+        <v>4016000</v>
       </c>
       <c r="I2" t="n">
-        <v>8896000</v>
+        <v>-34300000</v>
       </c>
       <c r="J2" t="n">
-        <v>-21156000</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
+        <v>-23811000</v>
+      </c>
+      <c r="K2" t="n">
+        <v>727000</v>
+      </c>
       <c r="L2" t="n">
-        <v>-2014000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-25000000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>26000000</v>
-      </c>
+        <v>15743000</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>-3014000</v>
+        <v>15743000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3014000</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>-39450000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>55193000</v>
+      </c>
       <c r="S2" t="n">
-        <v>13460000</v>
+        <v>-6294000</v>
       </c>
       <c r="T2" t="n">
-        <v>1275000</v>
+        <v>1480000</v>
       </c>
       <c r="U2" t="n">
-        <v>23577000</v>
+        <v>11139000</v>
       </c>
       <c r="V2" t="n">
-        <v>26047000</v>
+        <v>24163000</v>
       </c>
       <c r="W2" t="n">
-        <v>-2470000</v>
+        <v>-13024000</v>
       </c>
       <c r="X2" t="n">
-        <v>-8528000</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+        <v>-360000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
       <c r="Z2" t="n">
-        <v>-8528000</v>
+        <v>-360000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>-2395000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>-2395000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-2864000</v>
+        <v>-16158000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-2864000</v>
+        <v>-16158000</v>
       </c>
       <c r="AE2" t="n">
-        <v>16592000</v>
+        <v>-4195000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1040000</v>
+        <v>-4100000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-6913000</v>
+        <v>-5160000</v>
       </c>
       <c r="AH2" t="n">
-        <v>10267000</v>
+        <v>-87161000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-22330000</v>
+        <v>-1549000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-2400000</v>
+        <v>-21264000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-915000</v>
+        <v>-30730000</v>
       </c>
       <c r="AL2" t="n">
-        <v>35912000</v>
+        <v>-33618000</v>
       </c>
       <c r="AM2" t="n">
-        <v>5638000</v>
+        <v>296000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>15307000</v>
       </c>
       <c r="AO2" t="n">
-        <v>23146000</v>
+        <v>59463000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>2109000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>23146000</v>
+        <v>57354000</v>
       </c>
       <c r="AR2" t="n">
-        <v>329000</v>
+        <v>550000</v>
       </c>
       <c r="AS2" t="n">
-        <v>291000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
+        <v>1138000</v>
+      </c>
+      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="n">
-        <v>-15304000</v>
+        <v>9763000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-19458000</v>
+        <v>-10737000</v>
       </c>
       <c r="C3" t="n">
-        <v>-1976000</v>
+        <v>-53968000</v>
       </c>
       <c r="D3" t="n">
-        <v>8000000</v>
+        <v>63663000</v>
       </c>
       <c r="E3" t="n">
-        <v>-4295000</v>
+        <v>-10885000</v>
       </c>
       <c r="F3" t="n">
-        <v>46021000</v>
+        <v>160869000</v>
       </c>
       <c r="G3" t="n">
-        <v>160869000</v>
+        <v>198128000</v>
       </c>
       <c r="H3" t="n">
-        <v>-1577000</v>
+        <v>-8987000</v>
       </c>
       <c r="I3" t="n">
-        <v>-113271000</v>
+        <v>-28272000</v>
       </c>
       <c r="J3" t="n">
-        <v>-10783000</v>
+        <v>-21336000</v>
       </c>
       <c r="K3" t="n">
-        <v>7105000</v>
+        <v>1991000</v>
       </c>
       <c r="L3" t="n">
-        <v>6024000</v>
+        <v>9695000</v>
       </c>
       <c r="M3" t="n">
-        <v>7093000</v>
+        <v>12300000</v>
       </c>
       <c r="N3" t="n">
-        <v>-907000</v>
+        <v>-50683000</v>
       </c>
       <c r="O3" t="n">
-        <v>8000000</v>
+        <v>62983000</v>
       </c>
       <c r="P3" t="n">
-        <v>-1069000</v>
+        <v>-2605000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1069000</v>
+        <v>-3285000</v>
       </c>
       <c r="R3" t="n">
+        <v>680000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-7084000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1306000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2149000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>18919000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-16770000</v>
+      </c>
+      <c r="X3" t="n">
+        <v>346000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>346000</v>
+      </c>
+      <c r="Z3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="n">
-        <v>-87325000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>812000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-38595000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>12222000</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-50817000</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-45247000</v>
-      </c>
-      <c r="Y3" t="n">
+      <c r="AA3" t="n">
+        <v>-2094000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-2094000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-8791000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-8791000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>148000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-3707000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-4914000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-43613000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>20457000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-19852000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>2565000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>-46783000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>2684000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>6264000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>44675000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>2700000</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>41975000</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>2849000</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>535000</v>
+      </c>
+      <c r="AT3" t="n">
         <v>0</v>
       </c>
-      <c r="Z3" t="n">
-        <v>-45247000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-696000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>-696000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-3599000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-3599000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>-15163000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>-5892000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-6995000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-21179000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>-25987000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>21821000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>-3669000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>-13344000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>5621000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>2074000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>32581000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1803000</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>30778000</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>759000</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>408000</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>-10458000</v>
-      </c>
       <c r="AU3" t="n">
-        <v>-19136000</v>
+        <v>-9901000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-10737000</v>
+        <v>-19458000</v>
       </c>
       <c r="C4" t="n">
-        <v>-53968000</v>
+        <v>-1976000</v>
       </c>
       <c r="D4" t="n">
-        <v>63663000</v>
+        <v>8000000</v>
       </c>
       <c r="E4" t="n">
-        <v>-10885000</v>
+        <v>-4295000</v>
       </c>
       <c r="F4" t="n">
+        <v>46021000</v>
+      </c>
+      <c r="G4" t="n">
         <v>160869000</v>
       </c>
-      <c r="G4" t="n">
-        <v>198128000</v>
-      </c>
       <c r="H4" t="n">
-        <v>-8987000</v>
+        <v>-1577000</v>
       </c>
       <c r="I4" t="n">
-        <v>-28272000</v>
+        <v>-113271000</v>
       </c>
       <c r="J4" t="n">
-        <v>-21336000</v>
+        <v>-10783000</v>
       </c>
       <c r="K4" t="n">
-        <v>1991000</v>
+        <v>7105000</v>
       </c>
       <c r="L4" t="n">
-        <v>9695000</v>
+        <v>6024000</v>
       </c>
       <c r="M4" t="n">
-        <v>12300000</v>
+        <v>7093000</v>
       </c>
       <c r="N4" t="n">
-        <v>-50683000</v>
+        <v>-907000</v>
       </c>
       <c r="O4" t="n">
-        <v>62983000</v>
+        <v>8000000</v>
       </c>
       <c r="P4" t="n">
-        <v>-2605000</v>
+        <v>-1069000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3285000</v>
+        <v>-1069000</v>
       </c>
       <c r="R4" t="n">
-        <v>680000</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-7084000</v>
+        <v>-87325000</v>
       </c>
       <c r="T4" t="n">
-        <v>1306000</v>
+        <v>812000</v>
       </c>
       <c r="U4" t="n">
-        <v>2149000</v>
+        <v>-38595000</v>
       </c>
       <c r="V4" t="n">
-        <v>18919000</v>
+        <v>12222000</v>
       </c>
       <c r="W4" t="n">
-        <v>-16770000</v>
+        <v>-50817000</v>
       </c>
       <c r="X4" t="n">
-        <v>346000</v>
+        <v>-45247000</v>
       </c>
       <c r="Y4" t="n">
-        <v>346000</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-45247000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-2094000</v>
+        <v>-696000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-2094000</v>
+        <v>-696000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-8791000</v>
+        <v>-3599000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-8791000</v>
+        <v>-3599000</v>
       </c>
       <c r="AE4" t="n">
-        <v>148000</v>
+        <v>-15163000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-3707000</v>
+        <v>-5892000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-4914000</v>
+        <v>-6995000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-43613000</v>
+        <v>-21179000</v>
       </c>
       <c r="AI4" t="n">
-        <v>20457000</v>
+        <v>-25987000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-19852000</v>
+        <v>21821000</v>
       </c>
       <c r="AK4" t="n">
-        <v>2565000</v>
+        <v>-3669000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-46783000</v>
+        <v>-13344000</v>
       </c>
       <c r="AM4" t="n">
-        <v>2684000</v>
+        <v>5621000</v>
       </c>
       <c r="AN4" t="n">
-        <v>6264000</v>
+        <v>2074000</v>
       </c>
       <c r="AO4" t="n">
-        <v>44675000</v>
+        <v>32581000</v>
       </c>
       <c r="AP4" t="n">
-        <v>2700000</v>
+        <v>1803000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>41975000</v>
+        <v>30778000</v>
       </c>
       <c r="AR4" t="n">
-        <v>2849000</v>
+        <v>759000</v>
       </c>
       <c r="AS4" t="n">
-        <v>535000</v>
+        <v>408000</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>-10458000</v>
       </c>
       <c r="AU4" t="n">
-        <v>-9901000</v>
+        <v>-19136000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-22748000</v>
+        <v>13728000</v>
       </c>
       <c r="C5" t="n">
-        <v>-39450000</v>
+        <v>-28014000</v>
       </c>
       <c r="D5" t="n">
-        <v>55193000</v>
+        <v>26000000</v>
       </c>
       <c r="E5" t="n">
-        <v>-18553000</v>
+        <v>-2864000</v>
       </c>
       <c r="F5" t="n">
-        <v>198128000</v>
+        <v>53319000</v>
       </c>
       <c r="G5" t="n">
-        <v>228412000</v>
+        <v>46021000</v>
       </c>
       <c r="H5" t="n">
-        <v>4016000</v>
+        <v>-1598000</v>
       </c>
       <c r="I5" t="n">
-        <v>-34300000</v>
+        <v>8896000</v>
       </c>
       <c r="J5" t="n">
-        <v>-23811000</v>
-      </c>
-      <c r="K5" t="n">
-        <v>727000</v>
-      </c>
+        <v>-21156000</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>15743000</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+        <v>-2014000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-25000000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>26000000</v>
+      </c>
       <c r="P5" t="n">
-        <v>15743000</v>
+        <v>-3014000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-39450000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>55193000</v>
-      </c>
+        <v>-3014000</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>-6294000</v>
+        <v>13460000</v>
       </c>
       <c r="T5" t="n">
-        <v>1480000</v>
+        <v>1275000</v>
       </c>
       <c r="U5" t="n">
-        <v>11139000</v>
+        <v>23577000</v>
       </c>
       <c r="V5" t="n">
-        <v>24163000</v>
+        <v>26047000</v>
       </c>
       <c r="W5" t="n">
-        <v>-13024000</v>
+        <v>-2470000</v>
       </c>
       <c r="X5" t="n">
-        <v>-360000</v>
-      </c>
-      <c r="Y5" t="n">
+        <v>-8528000</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>-8528000</v>
+      </c>
+      <c r="AA5" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" t="n">
-        <v>-360000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-2395000</v>
-      </c>
       <c r="AB5" t="n">
-        <v>-2395000</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>-16158000</v>
+        <v>-2864000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-16158000</v>
+        <v>-2864000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-4195000</v>
+        <v>16592000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-4100000</v>
+        <v>-1040000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-5160000</v>
+        <v>-6913000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-87161000</v>
+        <v>10267000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-1549000</v>
+        <v>-22330000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-21264000</v>
+        <v>-2400000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-30730000</v>
+        <v>-915000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-33618000</v>
+        <v>35912000</v>
       </c>
       <c r="AM5" t="n">
-        <v>296000</v>
+        <v>5638000</v>
       </c>
       <c r="AN5" t="n">
-        <v>15307000</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>59463000</v>
+        <v>23146000</v>
       </c>
       <c r="AP5" t="n">
-        <v>2109000</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>57354000</v>
+        <v>23146000</v>
       </c>
       <c r="AR5" t="n">
-        <v>550000</v>
+        <v>329000</v>
       </c>
       <c r="AS5" t="n">
-        <v>1138000</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
+        <v>291000</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
       <c r="AU5" t="n">
-        <v>9763000</v>
+        <v>-15304000</v>
       </c>
     </row>
   </sheetData>
@@ -3682,187 +3682,187 @@
       </c>
       <c r="CZ1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="EK1" t="inlineStr">
@@ -3965,28 +3965,28 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="X2" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="AC2" t="n">
         <v>1560211200</v>
@@ -3995,31 +3995,31 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.146</v>
+        <v>-0.135</v>
       </c>
       <c r="AF2" t="n">
-        <v>9.857142</v>
+        <v>9.285714</v>
       </c>
       <c r="AG2" t="n">
-        <v>110000</v>
+        <v>40000</v>
       </c>
       <c r="AH2" t="n">
-        <v>110000</v>
+        <v>40000</v>
       </c>
       <c r="AI2" t="n">
-        <v>34031</v>
+        <v>28491</v>
       </c>
       <c r="AJ2" t="n">
-        <v>37100</v>
+        <v>22000</v>
       </c>
       <c r="AK2" t="n">
-        <v>37100</v>
+        <v>22000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.59</v>
+        <v>0.63</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.72</v>
+        <v>0.65</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -4028,10 +4028,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>298349920</v>
+        <v>281054240</v>
       </c>
       <c r="AQ2" t="n">
-        <v>289702083</v>
+        <v>298349907</v>
       </c>
       <c r="AR2" t="n">
         <v>0.149</v>
@@ -4046,13 +4046,13 @@
         <v>0.149</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.8184442</v>
+        <v>0.77099806</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.6984</v>
+        <v>0.6882</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.562875</v>
+        <v>0.5868</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -4069,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>279382912</v>
+        <v>262087264</v>
       </c>
       <c r="BD2" t="n">
         <v>0.0725</v>
@@ -4093,7 +4093,7 @@
         <v>1.022</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.6751468</v>
+        <v>0.63600785</v>
       </c>
       <c r="BL2" t="n">
         <v>1767139200</v>
@@ -4111,16 +4111,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.766</v>
+        <v>0.719</v>
       </c>
       <c r="BR2" t="n">
-        <v>-8.637</v>
+        <v>-8.103</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.6800001</v>
+        <v>2.2547169</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BU2" t="n">
         <v>0.015632</v>
@@ -4134,7 +4134,7 @@
         </is>
       </c>
       <c r="BX2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
@@ -4233,140 +4233,140 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CZ2" t="n">
-        <v>0.01999998</v>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>0.67 - 0.67</t>
-        </is>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DA2" t="n">
+        <v>1782112488</v>
       </c>
       <c r="DB2" t="inlineStr">
         <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>finmb_252332180</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DF2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>-5.7971044</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="DK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>1387503000000</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>-0.04000002</v>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>0.6 - 0.64</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>C CHENG HLDGS</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
           <t>C Cheng Holdings Limited</t>
         </is>
       </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>C CHENG HLDGS</t>
-        </is>
-      </c>
-      <c r="DD2" t="b">
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="DR2" t="n">
+        <v>-0.03820002</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>-0.05550715</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0.10770279</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DX2" t="b">
         <v>0</v>
       </c>
-      <c r="DE2" t="n">
-        <v>1387503000000</v>
-      </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DY2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DG2" t="n">
-        <v>34031</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>0.541</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>3.6308725</v>
-      </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="DZ2" t="n">
+        <v>28491</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>3.362416</v>
+      </c>
+      <c r="EC2" t="inlineStr">
         <is>
           <t>0.149 - 0.87</t>
         </is>
       </c>
-      <c r="DK2" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>-0.20689656</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>168</v>
-      </c>
-      <c r="DN2" t="n">
+      <c r="ED2" t="n">
+        <v>-0.22000003</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-0.2528736</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>225.47168</v>
+      </c>
+      <c r="EG2" t="n">
         <v>1742993098</v>
       </c>
-      <c r="DO2" t="n">
+      <c r="EH2" t="n">
         <v>1742993098</v>
       </c>
-      <c r="DP2" t="b">
+      <c r="EI2" t="b">
         <v>0</v>
       </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>finmb_252332180</t>
-        </is>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DU2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DX2" t="n">
+      <c r="EJ2" t="n">
         <v>0.07000000000000001</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-0.008400023</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-0.012027524</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>0.12712502</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>0.2258495</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>15</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EF2" t="n">
-        <v>1780285221</v>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>PRE</t>
-        </is>
-      </c>
-      <c r="EH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>2.9850717</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>0.6899999999999999</v>
       </c>
       <c r="EK2" t="inlineStr"/>
     </row>
